--- a/financial_models/opportunities/0386.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0386.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8F349B-5A59-4E11-90DF-21D93D810986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B2BA67-B2DD-4168-83E7-64179800BFE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="439">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2389,9 +2389,6 @@
   </si>
   <si>
     <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>N</t>
@@ -3785,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4273,13 +4270,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4344,7 +4341,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>17.696787580712193</v>
+        <v>0.80548127846515594</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4359,7 +4356,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>1.2976894231064677</v>
+        <v>-0.31663829693844048</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4379,22 +4376,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4406,13 +4403,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4420,7 +4417,7 @@
       </c>
       <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
-        <v>370950.79977478832</v>
+        <v>98885.132867871784</v>
       </c>
       <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4432,13 +4429,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4467,13 +4464,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4489,13 +4486,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4518,7 +4515,7 @@
       </c>
       <c r="C46" s="322">
         <f>Normalized_FCF!C47</f>
-        <v>0</v>
+        <v>-18601</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4533,7 +4530,7 @@
       </c>
       <c r="C47" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>0</v>
+        <v>-18601</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4551,7 +4548,7 @@
       </c>
       <c r="C50" s="188">
         <f>Normalized_FCF!C15</f>
-        <v>0</v>
+        <v>-15564.690847733797</v>
       </c>
       <c r="D50" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4559,13 +4556,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4573,7 +4570,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-92737.69994369708</v>
+        <v>-20071.033216967946</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4581,7 +4578,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4603,22 +4600,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4626,7 +4623,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>302168</v>
+        <v>25478</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4639,7 +4636,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>278213.09983109124</v>
+        <v>44648.408803170038</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4652,7 +4649,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.60941871295938521</v>
+        <v>9.7801202908963839E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4661,7 +4658,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>0.52016834539178136</v>
+        <v>6.7621884900931573E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4679,22 +4676,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4718,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4730,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4752,22 +4749,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4783,7 +4780,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>30.39475830884934</v>
+        <v>4.8778349950845721</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4804,13 +4801,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4823,13 +4820,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4837,7 +4834,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
-        <v>0</v>
+        <v>417043</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4850,7 +4847,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
+        <v>3.6449530800938588</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4863,7 +4860,7 @@
       </c>
       <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
-        <v>0.5</v>
+        <v>1.135394804633445</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -4872,7 +4869,7 @@
       </c>
       <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
-        <v>0</v>
+        <v>0.42716991722771752</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -4881,7 +4878,7 @@
       </c>
       <c r="C95" s="338">
         <f>BS!C50</f>
-        <v>0</v>
+        <v>4.2174489521821652</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -4895,7 +4892,7 @@
       </c>
       <c r="C98" s="188">
         <f>BS!C66</f>
-        <v>1</v>
+        <v>146799</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4908,7 +4905,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>-247267.57388162927</v>
+        <v>-104892.27115484935</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4921,7 +4918,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-2.1611169712168299</v>
+        <v>-0.91675776076785465</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4939,7 +4936,7 @@
       </c>
       <c r="C103" s="188">
         <f>Valuation_Model!C9</f>
-        <v>0</v>
+        <v>24725.9</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4952,7 +4949,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
+        <v>0.21610420355477192</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4960,13 +4957,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4974,7 +4971,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>28.233641337632509</v>
+        <v>0.53222835777762956</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4987,7 +4984,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>5.243996058095486E-6</v>
+        <v>-6.9537022109117581</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5005,13 +5002,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5037,15 +5034,15 @@
       </c>
       <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>39.51 HKD</v>
+        <v>1.19 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5059,15 +5056,15 @@
       </c>
       <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>32.35 HKD</v>
+        <v>0.77 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5085,11 +5082,11 @@
       </c>
       <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>30.2 HKD</v>
+        <v>0.69 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5107,11 +5104,11 @@
       </c>
       <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>28.23 HKD</v>
+        <v>0.53 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5129,11 +5126,11 @@
       </c>
       <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>28.23 HKD</v>
+        <v>0.53 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5146,7 +5143,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>30.598710239352997</v>
+        <v>0.69309519897662664</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5154,13 +5151,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5173,22 +5170,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5219,7 +5216,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0754716981132075</v>
+        <v>0.26981132075471698</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5255,7 +5252,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>3.7692908855128362</v>
+        <v>0.49000781511666869</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5265,7 +5262,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>13.927496695199357</v>
+        <v>0.31547346334848725</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5274,11 +5271,11 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>17.696787580712193</v>
+        <v>0.80548127846515594</v>
       </c>
       <c r="D139" s="342">
         <f>IF($D$11="","",C139*$E$22)</f>
-        <v>16.69508262331339</v>
+        <v>0.75988799855203382</v>
       </c>
     </row>
     <row r="140" spans="2:6">
@@ -5300,7 +5297,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.42164923154334921</v>
+        <v>-0.16215099982581083</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5324,7 +5321,7 @@
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>4.3719426974143953</v>
+        <v>0.56835255066387136</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5334,7 +5331,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>17.707586944070023</v>
+        <v>0.40109675866702932</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5343,11 +5340,11 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>22.07952964148442</v>
+        <v>0.96944930933090068</v>
       </c>
       <c r="D147" s="342">
         <f>IF($D$11="","",C147*$E$22)</f>
-        <v>20.829744944796619</v>
+        <v>0.91457482012349112</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -5369,7 +5366,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.27841632968281327</v>
+        <v>-0.39872460632005269</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5393,7 +5390,7 @@
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>5.3486918603257889</v>
+        <v>0.69532994184235264</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5403,7 +5400,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>24.290242721632399</v>
+        <v>0.55020131504393588</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5412,11 +5409,11 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>29.638934581958189</v>
+        <v>1.2455312568862884</v>
       </c>
       <c r="D155" s="342">
         <f>IF($D$11="","",C155*$E$22)</f>
-        <v>27.961259039583194</v>
+        <v>1.1750294876285738</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5438,7 +5435,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>3.1366539631478951E-2</v>
+        <v>-0.79705653527155884</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -5452,13 +5449,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5495,13 +5492,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5509,22 +5506,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5548,17 +5545,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5575,6 +5561,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5721,34 +5718,34 @@
         <v>43</v>
       </c>
       <c r="C5" s="181">
-        <v>2598935</v>
+        <v>2866250</v>
       </c>
       <c r="D5" s="181">
-        <v>2709656</v>
+        <v>2982577</v>
       </c>
       <c r="E5" s="181">
-        <v>2819363</v>
+        <v>3083354</v>
       </c>
       <c r="F5" s="181">
-        <v>2216551</v>
+        <v>2475583</v>
       </c>
       <c r="G5" s="181">
-        <v>1688398</v>
+        <v>1923345</v>
       </c>
       <c r="H5" s="181">
-        <v>2488852</v>
+        <v>2731387</v>
       </c>
       <c r="I5" s="181">
-        <v>2401012</v>
+        <v>2647510</v>
       </c>
       <c r="J5" s="181">
-        <v>1890398</v>
+        <v>2125690</v>
       </c>
       <c r="K5" s="181">
-        <v>1492165</v>
+        <v>1724171</v>
       </c>
       <c r="L5" s="181">
-        <v>1592771</v>
+        <v>1829114</v>
       </c>
       <c r="M5" s="181"/>
     </row>
@@ -5757,10 +5754,12 @@
         <v>54</v>
       </c>
       <c r="C6" s="181">
-        <v>119443</v>
+        <f>119443+9375</f>
+        <v>128818</v>
       </c>
       <c r="D6" s="181">
-        <v>120828</v>
+        <f>120828+11055</f>
+        <v>131883</v>
       </c>
       <c r="E6" s="181">
         <v>115775</v>
@@ -6275,10 +6274,13 @@
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C25" s="39">
-        <f>2.2/Exchange_Rate</f>
-        <v>2.0754716981132075</v>
-      </c>
-      <c r="D25" s="39"/>
+        <f>(0.14+0.146)/Exchange_Rate</f>
+        <v>0.26981132075471698</v>
+      </c>
+      <c r="D25" s="39">
+        <f>(0.2+0.145)/Exchange_Rate</f>
+        <v>0.32547169811320753</v>
+      </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -6294,7 +6296,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6303,7 +6305,7 @@
       </c>
       <c r="C28" s="183">
         <f>BS!C4</f>
-        <v>1</v>
+        <v>79069</v>
       </c>
       <c r="D28" s="181">
         <v>48652</v>
@@ -6340,7 +6342,7 @@
       </c>
       <c r="C29" s="183">
         <f>BS!C6</f>
-        <v>0</v>
+        <v>256595</v>
       </c>
       <c r="D29" s="181">
         <v>250898</v>
@@ -6377,7 +6379,7 @@
       </c>
       <c r="C30" s="186">
         <f>BS!C33+BS!C42</f>
-        <v>1</v>
+        <v>1108478</v>
       </c>
       <c r="D30" s="182">
         <v>1068019</v>
@@ -6414,7 +6416,7 @@
       </c>
       <c r="C31" s="186">
         <f>BS!G27</f>
-        <v>2</v>
+        <v>976293</v>
       </c>
       <c r="D31" s="182">
         <v>958655</v>
@@ -6451,7 +6453,7 @@
       </c>
       <c r="C32" s="183">
         <f>BS!G28</f>
-        <v>0</v>
+        <v>156371</v>
       </c>
       <c r="D32" s="181">
         <v>152861</v>
@@ -6558,43 +6560,43 @@
       </c>
       <c r="C37" s="183">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
-        <v>-2598935</v>
+        <v>-2866250</v>
       </c>
       <c r="D37" s="183">
         <f t="shared" si="2"/>
-        <v>-2709656</v>
+        <v>-2982577</v>
       </c>
       <c r="E37" s="183">
         <f t="shared" si="2"/>
-        <v>-2819363</v>
+        <v>-3083354</v>
       </c>
       <c r="F37" s="183">
         <f t="shared" si="2"/>
-        <v>-2216551</v>
+        <v>-2475583</v>
       </c>
       <c r="G37" s="183">
         <f t="shared" si="2"/>
-        <v>-1688398</v>
+        <v>-1923345</v>
       </c>
       <c r="H37" s="183">
         <f t="shared" si="2"/>
-        <v>-2488852</v>
+        <v>-2731387</v>
       </c>
       <c r="I37" s="183">
         <f t="shared" si="2"/>
-        <v>-2401012</v>
+        <v>-2647510</v>
       </c>
       <c r="J37" s="183">
         <f t="shared" si="2"/>
-        <v>-1890398</v>
+        <v>-2125690</v>
       </c>
       <c r="K37" s="183">
         <f t="shared" si="2"/>
-        <v>-1492165</v>
+        <v>-1724171</v>
       </c>
       <c r="L37" s="183">
         <f t="shared" si="2"/>
-        <v>-1592771</v>
+        <v>-1829114</v>
       </c>
       <c r="M37" s="183" t="str">
         <f t="shared" si="2"/>
@@ -6607,43 +6609,43 @@
       </c>
       <c r="C38" s="184">
         <f>IF(C36="","",C36+C37)</f>
-        <v>475627</v>
+        <v>208312</v>
       </c>
       <c r="D38" s="184">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
-        <v>502559</v>
+        <v>229638</v>
       </c>
       <c r="E38" s="184">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
-        <v>498805</v>
+        <v>234814</v>
       </c>
       <c r="F38" s="184">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
-        <v>524333</v>
+        <v>265301</v>
       </c>
       <c r="G38" s="184">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
-        <v>417586</v>
+        <v>182639</v>
       </c>
       <c r="H38" s="184">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
-        <v>477341</v>
+        <v>234806</v>
       </c>
       <c r="I38" s="184">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
-        <v>490167</v>
+        <v>243669</v>
       </c>
       <c r="J38" s="184">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
-        <v>469795</v>
+        <v>234503</v>
       </c>
       <c r="K38" s="184">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
-        <v>438746</v>
+        <v>206740</v>
       </c>
       <c r="L38" s="184">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
-        <v>426112</v>
+        <v>189769</v>
       </c>
       <c r="M38" s="184" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
@@ -6656,11 +6658,11 @@
       </c>
       <c r="C39" s="183">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
-        <v>-119443</v>
+        <v>-128818</v>
       </c>
       <c r="D39" s="183">
         <f t="shared" si="13"/>
-        <v>-120828</v>
+        <v>-131883</v>
       </c>
       <c r="E39" s="183">
         <f t="shared" si="13"/>
@@ -6754,11 +6756,11 @@
       </c>
       <c r="C41" s="185">
         <f>IF(C$4="","",C39-C40)</f>
-        <v>-58021</v>
+        <v>-67396</v>
       </c>
       <c r="D41" s="185">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
-        <v>-59664</v>
+        <v>-70719</v>
       </c>
       <c r="E41" s="185">
         <f t="shared" si="15"/>
@@ -6852,43 +6854,43 @@
       </c>
       <c r="C43" s="186">
         <f>IF(C$4="","",C38+C39+C42)</f>
-        <v>340969</v>
+        <v>64279</v>
       </c>
       <c r="D43" s="186">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
-        <v>367762</v>
+        <v>83786</v>
       </c>
       <c r="E43" s="186">
         <f t="shared" si="17"/>
-        <v>370257</v>
+        <v>106266</v>
       </c>
       <c r="F43" s="186">
         <f t="shared" si="17"/>
-        <v>392426</v>
+        <v>133394</v>
       </c>
       <c r="G43" s="186">
         <f t="shared" si="17"/>
-        <v>276771</v>
+        <v>41824</v>
       </c>
       <c r="H43" s="186">
         <f t="shared" si="17"/>
-        <v>342318</v>
+        <v>99783</v>
       </c>
       <c r="I43" s="186">
         <f t="shared" si="17"/>
-        <v>349425</v>
+        <v>102927</v>
       </c>
       <c r="J43" s="186">
         <f t="shared" si="17"/>
-        <v>334812</v>
+        <v>99520</v>
       </c>
       <c r="K43" s="186">
         <f t="shared" si="17"/>
-        <v>315041</v>
+        <v>83035</v>
       </c>
       <c r="L43" s="186">
         <f t="shared" si="17"/>
-        <v>307359</v>
+        <v>71016</v>
       </c>
       <c r="M43" s="186" t="str">
         <f t="shared" si="17"/>
@@ -6901,43 +6903,43 @@
       </c>
       <c r="C44" s="187">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
-        <v>-257790</v>
+        <v>18900</v>
       </c>
       <c r="D44" s="187">
         <f t="shared" si="18"/>
-        <v>-270405</v>
+        <v>13571</v>
       </c>
       <c r="E44" s="187">
         <f t="shared" si="18"/>
-        <v>-265239</v>
+        <v>-1248</v>
       </c>
       <c r="F44" s="187">
         <f t="shared" si="18"/>
-        <v>-274792</v>
+        <v>-15760</v>
       </c>
       <c r="G44" s="187">
         <f t="shared" si="18"/>
-        <v>-228802</v>
+        <v>6145</v>
       </c>
       <c r="H44" s="187">
         <f t="shared" si="18"/>
-        <v>-252302</v>
+        <v>-9767</v>
       </c>
       <c r="I44" s="187">
         <f t="shared" si="18"/>
-        <v>-248923</v>
+        <v>-2425</v>
       </c>
       <c r="J44" s="187">
         <f t="shared" si="18"/>
-        <v>-248239</v>
+        <v>-12947</v>
       </c>
       <c r="K44" s="187">
         <f t="shared" si="18"/>
-        <v>-235164</v>
+        <v>-3158</v>
       </c>
       <c r="L44" s="187">
         <f t="shared" si="18"/>
-        <v>-251400</v>
+        <v>-15057</v>
       </c>
       <c r="M44" s="187" t="str">
         <f t="shared" si="18"/>
@@ -7401,43 +7403,43 @@
       </c>
       <c r="C58" s="188">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
-        <v>-257790</v>
+        <v>18900</v>
       </c>
       <c r="D58" s="188">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
-        <v>-270405</v>
+        <v>13571</v>
       </c>
       <c r="E58" s="188">
         <f t="shared" si="28"/>
-        <v>-265239</v>
+        <v>-1248</v>
       </c>
       <c r="F58" s="188">
         <f t="shared" si="28"/>
-        <v>-274792</v>
+        <v>-15760</v>
       </c>
       <c r="G58" s="188">
         <f t="shared" si="28"/>
-        <v>-228802</v>
+        <v>6145</v>
       </c>
       <c r="H58" s="188">
         <f t="shared" si="28"/>
-        <v>-252302</v>
+        <v>-9767</v>
       </c>
       <c r="I58" s="188">
         <f t="shared" si="28"/>
-        <v>-248923</v>
+        <v>-2425</v>
       </c>
       <c r="J58" s="188">
         <f t="shared" si="28"/>
-        <v>-248239</v>
+        <v>-12947</v>
       </c>
       <c r="K58" s="188">
         <f t="shared" si="28"/>
-        <v>-235164</v>
+        <v>-3158</v>
       </c>
       <c r="L58" s="188">
         <f t="shared" si="28"/>
-        <v>-251400</v>
+        <v>-15057</v>
       </c>
       <c r="M58" s="188" t="str">
         <f t="shared" si="28"/>
@@ -7652,11 +7654,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0754716981132075</v>
+        <v>0.26981132075471698</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0</v>
+        <v>0.32547169811320753</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -7756,39 +7758,39 @@
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
-        <v>-5.3589727773256435E-2</v>
+        <v>-9.2867905137651419E-2</v>
       </c>
       <c r="D69" s="92">
         <f t="shared" ref="D69:M69" si="35">IF(E$36="","",D38/E38-1)</f>
-        <v>7.5259871091910568E-3</v>
+        <v>-2.2042978698033289E-2</v>
       </c>
       <c r="E69" s="92">
         <f t="shared" si="35"/>
-        <v>-4.8686617092572826E-2</v>
+        <v>-0.11491475720031208</v>
       </c>
       <c r="F69" s="92">
         <f t="shared" si="35"/>
-        <v>0.25562878065835548</v>
+        <v>0.45259774746905101</v>
       </c>
       <c r="G69" s="92">
         <f t="shared" si="35"/>
-        <v>-0.12518304524438506</v>
+        <v>-0.22217064299890121</v>
       </c>
       <c r="H69" s="92">
         <f t="shared" si="35"/>
-        <v>-2.6166592202249483E-2</v>
+        <v>-3.6373112706171051E-2</v>
       </c>
       <c r="I69" s="92">
         <f t="shared" si="35"/>
-        <v>4.3363594759416424E-2</v>
+        <v>3.9086919996759173E-2</v>
       </c>
       <c r="J69" s="92">
         <f t="shared" si="35"/>
-        <v>7.0767596741622807E-2</v>
+        <v>0.134289445680565</v>
       </c>
       <c r="K69" s="92">
         <f t="shared" si="35"/>
-        <v>2.9649481826374391E-2</v>
+        <v>8.9429780417244142E-2</v>
       </c>
       <c r="L69" s="92" t="str">
         <f t="shared" si="35"/>
@@ -7806,39 +7808,39 @@
       </c>
       <c r="C70" s="101">
         <f>IF(D$36="","",C43/D43-1)</f>
-        <v>-7.2854182868268058E-2</v>
+        <v>-0.23281932542429518</v>
       </c>
       <c r="D70" s="101">
         <f t="shared" ref="D70:M70" si="36">IF(E$36="","",D43/E43-1)</f>
-        <v>-6.7385626740344984E-3</v>
+        <v>-0.21154461445805806</v>
       </c>
       <c r="E70" s="101">
         <f t="shared" si="36"/>
-        <v>-5.649217941726592E-2</v>
+        <v>-0.20336746780214998</v>
       </c>
       <c r="F70" s="101">
         <f t="shared" si="36"/>
-        <v>0.41787253722391426</v>
+        <v>2.1894127773527163</v>
       </c>
       <c r="G70" s="101">
         <f t="shared" si="36"/>
-        <v>-0.19147985206737594</v>
+        <v>-0.58085044546666265</v>
       </c>
       <c r="H70" s="101">
         <f t="shared" si="36"/>
-        <v>-2.0339128568362286E-2</v>
+        <v>-3.0545920895391876E-2</v>
       </c>
       <c r="I70" s="101">
         <f t="shared" si="36"/>
-        <v>4.3645389054155714E-2</v>
+        <v>3.423432475884236E-2</v>
       </c>
       <c r="J70" s="101">
         <f t="shared" si="36"/>
-        <v>6.2756911005234173E-2</v>
+        <v>0.19853074004937676</v>
       </c>
       <c r="K70" s="101">
         <f t="shared" si="36"/>
-        <v>2.4993574289349008E-2</v>
+        <v>0.169243550749127</v>
       </c>
       <c r="L70" s="101" t="str">
         <f t="shared" si="36"/>
@@ -7855,39 +7857,39 @@
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
-        <v>-4.6652243856437514E-2</v>
+        <v>0.39267555817552124</v>
       </c>
       <c r="D71" s="101">
         <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D44/E44-1)</f>
-        <v>1.9476773777611811E-2</v>
+        <v>-11.874198717948717</v>
       </c>
       <c r="E71" s="101">
         <f t="shared" si="37"/>
-        <v>-3.4764476403970956E-2</v>
+        <v>-0.92081218274111676</v>
       </c>
       <c r="F71" s="101">
         <f t="shared" si="37"/>
-        <v>0.20100348773175059</v>
+        <v>-3.5646867371847031</v>
       </c>
       <c r="G71" s="101">
         <f t="shared" si="37"/>
-        <v>-9.3142345284619177E-2</v>
+        <v>-1.6291594143544588</v>
       </c>
       <c r="H71" s="101">
         <f t="shared" si="37"/>
-        <v>1.3574478854907035E-2</v>
+        <v>3.0276288659793815</v>
       </c>
       <c r="I71" s="101">
         <f t="shared" si="37"/>
-        <v>2.7554091017125693E-3</v>
+        <v>-0.81269792229860194</v>
       </c>
       <c r="J71" s="101">
         <f t="shared" si="37"/>
-        <v>5.5599496521576475E-2</v>
+        <v>3.09974667511083</v>
       </c>
       <c r="K71" s="101">
         <f t="shared" si="37"/>
-        <v>-6.4582338902147929E-2</v>
+        <v>-0.79026366474065224</v>
       </c>
       <c r="L71" s="101" t="str">
         <f t="shared" si="37"/>
@@ -7976,7 +7978,7 @@
       </c>
       <c r="C76" s="188">
         <f>IF(C$4="","",C79+C80)</f>
-        <v>3</v>
+        <v>2084771</v>
       </c>
       <c r="D76" s="188">
         <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
@@ -8025,7 +8027,7 @@
       </c>
       <c r="C77" s="185">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
-        <v>1</v>
+        <v>79069</v>
       </c>
       <c r="D77" s="185">
         <f t="shared" si="40"/>
@@ -8059,7 +8061,7 @@
       </c>
       <c r="C78" s="185">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>256595</v>
       </c>
       <c r="D78" s="185">
         <f t="shared" si="40"/>
@@ -8093,7 +8095,7 @@
       </c>
       <c r="C79" s="183">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
-        <v>1</v>
+        <v>1108478</v>
       </c>
       <c r="D79" s="183">
         <f t="shared" si="41"/>
@@ -8142,7 +8144,7 @@
       </c>
       <c r="C80" s="183">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
-        <v>2</v>
+        <v>976293</v>
       </c>
       <c r="D80" s="183">
         <f t="shared" si="42"/>
@@ -8280,7 +8282,8 @@
         <v>24</v>
       </c>
       <c r="C4" s="19">
-        <v>1</v>
+        <f>44333+2613+32123</f>
+        <v>79069</v>
       </c>
       <c r="D4" s="294">
         <v>0.6</v>
@@ -8290,7 +8293,7 @@
         <v>78</v>
       </c>
       <c r="G4" s="19">
-        <v>1</v>
+        <v>146799</v>
       </c>
       <c r="H4" s="294">
         <v>0.9</v>
@@ -8301,7 +8304,7 @@
         <v>33</v>
       </c>
       <c r="C5" s="19">
-        <v>0</v>
+        <v>2554</v>
       </c>
       <c r="D5" s="294">
         <v>0.6</v>
@@ -8322,7 +8325,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="19">
-        <v>0</v>
+        <v>256595</v>
       </c>
       <c r="D6" s="294">
         <v>0.5</v>
@@ -8353,7 +8356,7 @@
         <v>179</v>
       </c>
       <c r="G7" s="19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="294">
         <v>0.6</v>
@@ -8385,7 +8388,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="19">
-        <v>0</v>
+        <v>6429</v>
       </c>
       <c r="D9" s="294">
         <v>0.1</v>
@@ -8418,7 +8421,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="19">
-        <v>0</v>
+        <v>33065</v>
       </c>
       <c r="D11" s="294">
         <v>0.05</v>
@@ -8431,22 +8434,22 @@
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
-        <v>1</v>
+        <v>377712</v>
       </c>
       <c r="D12" s="20">
         <f>C4*D4+C5*D5+C9*D9+C6*D6+C8*D8+C7*D7+C10*D10+C11*D11</f>
-        <v>0.6</v>
+        <v>179567.45</v>
       </c>
       <c r="F12" s="80" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
-        <v>1</v>
+        <v>146803</v>
       </c>
       <c r="H12" s="20">
         <f>G4*H4+G5*H5+G6*H6+G7*H7+G8*H8+G9*H9</f>
-        <v>0.9</v>
+        <v>132121.5</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1">
@@ -8559,7 +8562,8 @@
         <v>26</v>
       </c>
       <c r="C19" s="19">
-        <v>1</v>
+        <f>717105+208747+164342</f>
+        <v>1090194</v>
       </c>
       <c r="D19" s="294">
         <v>0.1</v>
@@ -8568,7 +8572,8 @@
         <v>183</v>
       </c>
       <c r="G19" s="19">
-        <v>0</v>
+        <f>246819+416</f>
+        <v>247235</v>
       </c>
       <c r="H19" s="294">
         <v>0.1</v>
@@ -8599,7 +8604,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="19">
-        <v>0</v>
+        <v>137983</v>
       </c>
       <c r="D21" s="294">
         <v>0.05</v>
@@ -8619,7 +8624,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="19">
-        <v>0</v>
+        <v>18777</v>
       </c>
       <c r="D22" s="294">
         <v>0.9</v>
@@ -8631,7 +8636,8 @@
         <v>21</v>
       </c>
       <c r="C23" s="19">
-        <v>0</v>
+        <f>6493+12131+47443</f>
+        <v>66067</v>
       </c>
       <c r="D23" s="294">
         <v>0</v>
@@ -8644,22 +8650,22 @@
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
-        <v>1</v>
+        <v>1313021</v>
       </c>
       <c r="D24" s="20">
         <f>C15*D15+C16*D16+C18*D18+C17*D17+C19*D19+C20*D20+C21*D21+C22*D22+C23*D23</f>
-        <v>0.1</v>
+        <v>132817.85</v>
       </c>
       <c r="F24" s="80" t="s">
         <v>71</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
-        <v>0</v>
+        <v>247235</v>
       </c>
       <c r="H24" s="20">
         <f>G15*H15+G16*H16+G17*H17+G18*H18+G19*H19+G20*H20+G21*H21</f>
-        <v>0</v>
+        <v>24723.5</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
@@ -8684,18 +8690,18 @@
         <v>5</v>
       </c>
       <c r="C27" s="19">
-        <v>0</v>
+        <v>48231</v>
       </c>
       <c r="F27" s="208" t="s">
         <v>30</v>
       </c>
       <c r="G27" s="85">
         <f>G32-G30</f>
-        <v>2</v>
+        <v>976293</v>
       </c>
       <c r="H27" s="209">
         <f>H32-G30</f>
-        <v>0.60000000000000009</v>
+        <v>-639247.69999999995</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
@@ -8708,8 +8714,8 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
-        <v>0</v>
+      <c r="G28" s="12">
+        <v>156371</v>
       </c>
       <c r="H28" s="209"/>
     </row>
@@ -8725,11 +8731,11 @@
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
-        <v>2</v>
+        <v>819922</v>
       </c>
       <c r="H29" s="209">
         <f>H27-G28</f>
-        <v>0.60000000000000009</v>
+        <v>-795618.7</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
@@ -8737,14 +8743,14 @@
         <v>8</v>
       </c>
       <c r="C30" s="19">
-        <v>0</v>
+        <v>3412</v>
       </c>
       <c r="F30" s="208" t="s">
         <v>23</v>
       </c>
       <c r="G30" s="85">
         <f>C33+C42</f>
-        <v>1</v>
+        <v>1108478</v>
       </c>
       <c r="H30" s="209"/>
     </row>
@@ -8754,14 +8760,14 @@
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
-        <v>0</v>
+        <v>51643</v>
       </c>
       <c r="F31" s="211" t="s">
         <v>77</v>
       </c>
       <c r="G31" s="212">
         <f>C31+C40</f>
-        <v>0</v>
+        <v>417043</v>
       </c>
       <c r="H31" s="209"/>
     </row>
@@ -8771,18 +8777,18 @@
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
-        <v>1</v>
+        <v>621594</v>
       </c>
       <c r="F32" s="213" t="s">
         <v>75</v>
       </c>
       <c r="G32" s="214">
         <f>G35+G40</f>
-        <v>3</v>
+        <v>2084771</v>
       </c>
       <c r="H32" s="209">
         <f>H35+H40</f>
-        <v>1.6</v>
+        <v>469230.30000000005</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
@@ -8790,7 +8796,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="84">
-        <v>1</v>
+        <v>673237</v>
       </c>
       <c r="F33" s="215"/>
       <c r="G33" s="2"/>
@@ -8821,11 +8827,11 @@
       </c>
       <c r="G35" s="214">
         <f>C12+C24</f>
-        <v>2</v>
+        <v>1690733</v>
       </c>
       <c r="H35" s="221">
         <f>D12+D24</f>
-        <v>0.7</v>
+        <v>312385.30000000005</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
@@ -8833,14 +8839,14 @@
         <v>13</v>
       </c>
       <c r="C36" s="19">
-        <v>0</v>
+        <v>184934</v>
       </c>
       <c r="F36" s="211" t="s">
         <v>198</v>
       </c>
       <c r="G36" s="212">
         <f>C4+C15</f>
-        <v>1</v>
+        <v>79069</v>
       </c>
       <c r="H36" s="216"/>
     </row>
@@ -8849,14 +8855,14 @@
         <v>14</v>
       </c>
       <c r="C37" s="19">
-        <v>0</v>
+        <v>154904</v>
       </c>
       <c r="F37" s="211" t="s">
         <v>199</v>
       </c>
       <c r="G37" s="212">
         <f>C6</f>
-        <v>0</v>
+        <v>256595</v>
       </c>
       <c r="H37" s="216"/>
     </row>
@@ -8881,18 +8887,18 @@
         <v>16</v>
       </c>
       <c r="C39" s="19">
-        <v>0</v>
+        <v>25562</v>
       </c>
       <c r="F39" s="211" t="s">
         <v>80</v>
       </c>
       <c r="G39" s="212">
         <f>C7+C17+C19+C20</f>
-        <v>1</v>
+        <v>1090194</v>
       </c>
       <c r="H39" s="209">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
-        <v>0.1</v>
+        <v>109019.40000000001</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
@@ -8901,18 +8907,18 @@
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
-        <v>0</v>
+        <v>365400</v>
       </c>
       <c r="F40" s="220" t="s">
         <v>139</v>
       </c>
       <c r="G40" s="214">
         <f>G12+G24</f>
-        <v>1</v>
+        <v>394038</v>
       </c>
       <c r="H40" s="221">
         <f>H12+H24</f>
-        <v>0.9</v>
+        <v>156845</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1">
@@ -8921,18 +8927,18 @@
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
-        <v>0</v>
+        <v>69841</v>
       </c>
       <c r="F41" s="211" t="s">
         <v>192</v>
       </c>
       <c r="G41" s="212">
         <f>C70</f>
-        <v>1</v>
+        <v>146799</v>
       </c>
       <c r="H41" s="221">
         <f>H40-H42</f>
-        <v>0.9</v>
+        <v>132119.1</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
@@ -8940,18 +8946,18 @@
         <v>22</v>
       </c>
       <c r="C42" s="84">
-        <v>0</v>
+        <v>435241</v>
       </c>
       <c r="F42" s="222" t="s">
         <v>193</v>
       </c>
       <c r="G42" s="223">
         <f>C82</f>
-        <v>0</v>
+        <v>247239</v>
       </c>
       <c r="H42" s="224">
         <f>D82</f>
-        <v>0</v>
+        <v>24725.9</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
@@ -8985,11 +8991,11 @@
       </c>
       <c r="C46" s="188">
         <f>G29</f>
-        <v>2</v>
+        <v>819922</v>
       </c>
       <c r="D46" s="188">
         <f>H29</f>
-        <v>0.60000000000000009</v>
+        <v>-795618.7</v>
       </c>
       <c r="F46" s="283"/>
     </row>
@@ -9000,11 +9006,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7479986860318283E-5</v>
+        <v>7.1661128932429436</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>5.243996058095486E-6</v>
+        <v>-6.9537022109117581</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9030,11 +9036,11 @@
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
-        <v>0</v>
+        <v>4.2174489521821652</v>
       </c>
       <c r="D50" s="95">
         <f>G31/Normalized_FCF!G8</f>
-        <v>0</v>
+        <v>6.4880131924889932</v>
       </c>
       <c r="F50" s="283"/>
     </row>
@@ -9045,7 +9051,7 @@
       <c r="C51" s="202"/>
       <c r="D51" s="92">
         <f>G29/G32</f>
-        <v>0.66666666666666663</v>
+        <v>0.39329115763793721</v>
       </c>
       <c r="F51" s="283"/>
     </row>
@@ -9070,11 +9076,11 @@
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
-        <v>185475.39988739416</v>
+        <v>5.8486545698150913E-2</v>
       </c>
       <c r="D54" s="92">
         <f>Normalized_FCF!G8/G35</f>
-        <v>170484.5</v>
+        <v>3.8018421595840381E-2</v>
       </c>
       <c r="F54" s="283"/>
     </row>
@@ -9114,7 +9120,7 @@
       <c r="C58" s="98"/>
       <c r="D58" s="23">
         <f>Normalized_FCF!G9/BS!$G$39</f>
-        <v>120714</v>
+        <v>0.1107270816019901</v>
       </c>
       <c r="F58" s="5"/>
     </row>
@@ -9125,7 +9131,7 @@
       <c r="C59" s="98"/>
       <c r="D59" s="92">
         <f>G39/G32</f>
-        <v>0.33333333333333331</v>
+        <v>0.52293225490953199</v>
       </c>
       <c r="F59" s="283"/>
     </row>
@@ -9150,11 +9156,11 @@
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
-        <v>0</v>
+        <v>0.19071448259712509</v>
       </c>
       <c r="D62" s="92">
         <f>G28/G29</f>
-        <v>0</v>
+        <v>0.19071448259712509</v>
       </c>
       <c r="F62" s="283" t="s">
         <v>273</v>
@@ -9191,11 +9197,11 @@
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
-        <v>1</v>
+        <v>146799</v>
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>-247267.57388162927</v>
+        <v>-104892.27115484935</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9237,7 +9243,7 @@
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
-        <v>1</v>
+        <v>146799</v>
       </c>
       <c r="F70" s="283"/>
     </row>
@@ -9262,11 +9268,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-248775.78636286163</v>
+        <v>-253583.84472717202</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-247268.57388162927</v>
+        <v>-251691.27115484935</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9278,11 +9284,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>4.0196838069337299E-6</v>
+        <v>0.57889728802692209</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>4.0441855764441506E-6</v>
+        <v>0.58325026261909607</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9295,7 +9301,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>247268.57388162927</v>
+        <v>251691.27115484935</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9335,11 +9341,11 @@
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D79" s="188">
         <f>G7*H7+G17*H17</f>
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="F79" s="283"/>
     </row>
@@ -9349,11 +9355,11 @@
       </c>
       <c r="C80" s="20">
         <f>G19</f>
-        <v>0</v>
+        <v>247235</v>
       </c>
       <c r="D80" s="188">
         <f>G19*H19</f>
-        <v>0</v>
+        <v>24723.5</v>
       </c>
       <c r="F80" s="283"/>
     </row>
@@ -9377,11 +9383,11 @@
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
-        <v>0</v>
+        <v>247239</v>
       </c>
       <c r="D82" s="81">
         <f>SUM(D79:D81)</f>
-        <v>0</v>
+        <v>24725.9</v>
       </c>
       <c r="F82" s="283"/>
     </row>
@@ -9410,11 +9416,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>0</v>
+        <v>-442065.58</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0</v>
+        <v>-3.6449530800938588</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9427,11 +9433,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-262103.62831452704</v>
+        <v>-111185.80742414032</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-2.1611169712168299</v>
+        <v>-0.91675776076785465</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9444,11 +9450,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>0</v>
+        <v>26209.454000000002</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0</v>
+        <v>0.21610420355477192</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9461,11 +9467,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-262103.62831452704</v>
+        <v>-527041.93342414033</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-2.1611169712168299</v>
+        <v>-4.3456066373069415</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9656,48 +9662,48 @@
       </c>
       <c r="C5" s="191">
         <f>C25</f>
-        <v>-2642789.9502252117</v>
+        <v>-2909748.1171321282</v>
       </c>
       <c r="E5" s="302"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
-        <v>-2660357</v>
+        <v>-2927672</v>
       </c>
       <c r="H5" s="183">
         <f t="shared" si="1"/>
-        <v>-2770820</v>
+        <v>-3043741</v>
       </c>
       <c r="I5" s="183">
         <f t="shared" si="1"/>
-        <v>-2877930</v>
+        <v>-3141921</v>
       </c>
       <c r="J5" s="183">
         <f t="shared" si="1"/>
-        <v>-2274442</v>
+        <v>-2533474</v>
       </c>
       <c r="K5" s="183">
         <f t="shared" si="1"/>
-        <v>-1752836</v>
+        <v>-1987783</v>
       </c>
       <c r="L5" s="183">
         <f t="shared" si="1"/>
-        <v>-2552368</v>
+        <v>-2794903</v>
       </c>
       <c r="M5" s="183">
         <f t="shared" si="1"/>
-        <v>-2460408</v>
+        <v>-2706906</v>
       </c>
       <c r="N5" s="183">
         <f t="shared" si="1"/>
-        <v>-1946453</v>
+        <v>-2181745</v>
       </c>
       <c r="O5" s="183">
         <f t="shared" si="1"/>
-        <v>-1541715</v>
+        <v>-1773721</v>
       </c>
       <c r="P5" s="183">
         <f t="shared" si="1"/>
-        <v>-1639643</v>
+        <v>-1875986</v>
       </c>
       <c r="Q5" s="183" t="str">
         <f t="shared" si="1"/>
@@ -9711,48 +9717,48 @@
       </c>
       <c r="C6" s="184">
         <f>C4+C5</f>
-        <v>443667.29977478832</v>
+        <v>176709.13286787178</v>
       </c>
       <c r="E6" s="302"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
-        <v>414205</v>
+        <v>146890</v>
       </c>
       <c r="H6" s="184">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
-        <v>441395</v>
+        <v>168474</v>
       </c>
       <c r="I6" s="184">
         <f t="shared" si="2"/>
-        <v>440238</v>
+        <v>176247</v>
       </c>
       <c r="J6" s="184">
         <f t="shared" si="2"/>
-        <v>466442</v>
+        <v>207410</v>
       </c>
       <c r="K6" s="184">
         <f t="shared" si="2"/>
-        <v>353148</v>
+        <v>118201</v>
       </c>
       <c r="L6" s="184">
         <f t="shared" si="2"/>
-        <v>413825</v>
+        <v>171290</v>
       </c>
       <c r="M6" s="184">
         <f t="shared" si="2"/>
-        <v>430771</v>
+        <v>184273</v>
       </c>
       <c r="N6" s="184">
         <f t="shared" si="2"/>
-        <v>413740</v>
+        <v>178448</v>
       </c>
       <c r="O6" s="184">
         <f t="shared" si="2"/>
-        <v>389196</v>
+        <v>157190</v>
       </c>
       <c r="P6" s="184">
         <f t="shared" si="2"/>
-        <v>379240</v>
+        <v>142897</v>
       </c>
       <c r="Q6" s="184" t="str">
         <f t="shared" si="2"/>
@@ -9766,16 +9772,16 @@
       </c>
       <c r="C7" s="191">
         <f>C35</f>
-        <v>-72716.5</v>
+        <v>-77824</v>
       </c>
       <c r="E7" s="302"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
-        <v>-73236</v>
+        <v>-82611</v>
       </c>
       <c r="H7" s="191">
         <f t="shared" si="3"/>
-        <v>-73633</v>
+        <v>-84688</v>
       </c>
       <c r="I7" s="191">
         <f t="shared" si="3"/>
@@ -9821,50 +9827,50 @@
       </c>
       <c r="C8" s="192">
         <f>C6+C7</f>
-        <v>370950.79977478832</v>
+        <v>98885.132867871784</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="308"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
-        <v>340969</v>
+        <v>64279</v>
       </c>
       <c r="H8" s="184">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
-        <v>367762</v>
+        <v>83786</v>
       </c>
       <c r="I8" s="184">
         <f t="shared" si="4"/>
-        <v>370257</v>
+        <v>106266</v>
       </c>
       <c r="J8" s="184">
         <f t="shared" si="4"/>
-        <v>392426</v>
+        <v>133394</v>
       </c>
       <c r="K8" s="184">
         <f t="shared" si="4"/>
-        <v>276771</v>
+        <v>41824</v>
       </c>
       <c r="L8" s="184">
         <f t="shared" si="4"/>
-        <v>342318</v>
+        <v>99783</v>
       </c>
       <c r="M8" s="184">
         <f t="shared" si="4"/>
-        <v>349425</v>
+        <v>102927</v>
       </c>
       <c r="N8" s="184">
         <f t="shared" si="4"/>
-        <v>334812</v>
+        <v>99520</v>
       </c>
       <c r="O8" s="184">
         <f t="shared" si="4"/>
-        <v>315041</v>
+        <v>83035</v>
       </c>
       <c r="P8" s="184">
         <f t="shared" si="4"/>
-        <v>307359</v>
+        <v>71016</v>
       </c>
       <c r="Q8" s="184" t="str">
         <f t="shared" si="4"/>
@@ -10045,7 +10051,7 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>0</v>
+        <v>-18601</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
@@ -10100,48 +10106,48 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>370950.79977478832</v>
+        <v>80284.132867871784</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>322368</v>
+        <v>45678</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>463443</v>
+        <v>179467</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>463394</v>
+        <v>199403</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>493088</v>
+        <v>234056</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>276771</v>
+        <v>41824</v>
       </c>
       <c r="L13" s="184">
         <f t="shared" si="7"/>
-        <v>342318</v>
+        <v>99783</v>
       </c>
       <c r="M13" s="184">
         <f t="shared" si="7"/>
-        <v>349425</v>
+        <v>102927</v>
       </c>
       <c r="N13" s="184">
         <f t="shared" si="7"/>
-        <v>334812</v>
+        <v>99520</v>
       </c>
       <c r="O13" s="184">
         <f t="shared" si="7"/>
-        <v>315041</v>
+        <v>83035</v>
       </c>
       <c r="P13" s="184">
         <f t="shared" si="7"/>
-        <v>307359</v>
+        <v>71016</v>
       </c>
       <c r="Q13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -10155,7 +10161,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-92737.69994369708</v>
+        <v>-20071.033216967946</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10210,7 +10216,7 @@
       </c>
       <c r="C15" s="191">
         <f>-C4*C83</f>
-        <v>0</v>
+        <v>-15564.690847733797</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="309"/>
@@ -10267,50 +10273,50 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>278213.09983109124</v>
+        <v>44648.408803170038</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>302168</v>
+        <v>25478</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>437790</v>
+        <v>153814</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>435181</v>
+        <v>171190</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>455948</v>
+        <v>196916</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>261726</v>
+        <v>26779</v>
       </c>
       <c r="L16" s="184">
         <f t="shared" si="8"/>
-        <v>309893</v>
+        <v>67358</v>
       </c>
       <c r="M16" s="184">
         <f t="shared" si="8"/>
-        <v>312012</v>
+        <v>65514</v>
       </c>
       <c r="N16" s="184">
         <f t="shared" si="8"/>
-        <v>299358</v>
+        <v>64066</v>
       </c>
       <c r="O16" s="184">
         <f t="shared" si="8"/>
-        <v>281580</v>
+        <v>49574</v>
       </c>
       <c r="P16" s="184">
         <f t="shared" si="8"/>
-        <v>283607</v>
+        <v>47264</v>
       </c>
       <c r="Q16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -10375,50 +10381,50 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>278213.09983109124</v>
+        <v>44648.408803170038</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>302168</v>
+        <v>25478</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>437790</v>
+        <v>153814</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>435181</v>
+        <v>171190</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>455948</v>
+        <v>196916</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>261726</v>
+        <v>26779</v>
       </c>
       <c r="L19" s="186">
         <f t="shared" si="9"/>
-        <v>309893</v>
+        <v>67358</v>
       </c>
       <c r="M19" s="186">
         <f t="shared" si="9"/>
-        <v>312012</v>
+        <v>65514</v>
       </c>
       <c r="N19" s="186">
         <f t="shared" si="9"/>
-        <v>299358</v>
+        <v>64066</v>
       </c>
       <c r="O19" s="186">
         <f t="shared" si="9"/>
-        <v>281580</v>
+        <v>49574</v>
       </c>
       <c r="P19" s="186">
         <f t="shared" si="9"/>
-        <v>283607</v>
+        <v>47264</v>
       </c>
       <c r="Q19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10495,50 +10501,50 @@
       </c>
       <c r="C23" s="197">
         <f>-C4*C28</f>
-        <v>-2582765.8903351119</v>
+        <v>-2849724.0572420279</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="301"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
-        <v>-2598935</v>
+        <v>-2866250</v>
       </c>
       <c r="H23" s="183">
         <f>Data!D37</f>
-        <v>-2709656</v>
+        <v>-2982577</v>
       </c>
       <c r="I23" s="183">
         <f>Data!E37</f>
-        <v>-2819363</v>
+        <v>-3083354</v>
       </c>
       <c r="J23" s="183">
         <f>Data!F37</f>
-        <v>-2216551</v>
+        <v>-2475583</v>
       </c>
       <c r="K23" s="183">
         <f>Data!G37</f>
-        <v>-1688398</v>
+        <v>-1923345</v>
       </c>
       <c r="L23" s="183">
         <f>Data!H37</f>
-        <v>-2488852</v>
+        <v>-2731387</v>
       </c>
       <c r="M23" s="183">
         <f>Data!I37</f>
-        <v>-2401012</v>
+        <v>-2647510</v>
       </c>
       <c r="N23" s="183">
         <f>Data!J37</f>
-        <v>-1890398</v>
+        <v>-2125690</v>
       </c>
       <c r="O23" s="183">
         <f>Data!K37</f>
-        <v>-1492165</v>
+        <v>-1724171</v>
       </c>
       <c r="P23" s="183">
         <f>Data!L37</f>
-        <v>-1592771</v>
+        <v>-1829114</v>
       </c>
       <c r="Q23" s="183" t="str">
         <f>Data!M37</f>
@@ -10609,50 +10615,50 @@
       </c>
       <c r="C25" s="184">
         <f>C23+C24</f>
-        <v>-2642789.9502252117</v>
+        <v>-2909748.1171321282</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="307"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
-        <v>-2660357</v>
+        <v>-2927672</v>
       </c>
       <c r="H25" s="184">
         <f t="shared" si="10"/>
-        <v>-2770820</v>
+        <v>-3043741</v>
       </c>
       <c r="I25" s="184">
         <f t="shared" si="10"/>
-        <v>-2877930</v>
+        <v>-3141921</v>
       </c>
       <c r="J25" s="184">
         <f t="shared" si="10"/>
-        <v>-2274442</v>
+        <v>-2533474</v>
       </c>
       <c r="K25" s="184">
         <f t="shared" si="10"/>
-        <v>-1752836</v>
+        <v>-1987783</v>
       </c>
       <c r="L25" s="184">
         <f t="shared" si="10"/>
-        <v>-2552368</v>
+        <v>-2794903</v>
       </c>
       <c r="M25" s="184">
         <f t="shared" si="10"/>
-        <v>-2460408</v>
+        <v>-2706906</v>
       </c>
       <c r="N25" s="184">
         <f t="shared" si="10"/>
-        <v>-1946453</v>
+        <v>-2181745</v>
       </c>
       <c r="O25" s="184">
         <f t="shared" si="10"/>
-        <v>-1541715</v>
+        <v>-1773721</v>
       </c>
       <c r="P25" s="184">
         <f t="shared" si="10"/>
-        <v>-1639643</v>
+        <v>-1875986</v>
       </c>
       <c r="Q25" s="184" t="str">
         <f t="shared" si="10"/>
@@ -10677,7 +10683,7 @@
       </c>
       <c r="C28" s="63">
         <f>AVERAGE(G28:J28)</f>
-        <v>0.83680598211269952</v>
+        <v>0.92329937738228118</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
@@ -10686,43 +10692,43 @@
       <c r="F28" s="26"/>
       <c r="G28" s="13">
         <f t="shared" ref="G28:Q28" si="11">IF(G$4="","",ABS(G23/G$4))</f>
-        <v>0.84530251788710065</v>
+        <v>0.93224660943575055</v>
       </c>
       <c r="H28" s="13">
         <f t="shared" si="11"/>
-        <v>0.84354752094738361</v>
+        <v>0.92851101187187035</v>
       </c>
       <c r="I28" s="13">
         <f t="shared" si="11"/>
-        <v>0.84967457946674185</v>
+        <v>0.92923384228887751</v>
       </c>
       <c r="J28" s="13">
         <f t="shared" si="11"/>
-        <v>0.80869931014957219</v>
+        <v>0.9032060459326261</v>
       </c>
       <c r="K28" s="13">
         <f t="shared" si="11"/>
-        <v>0.80171454294049715</v>
+        <v>0.91327616923965238</v>
       </c>
       <c r="L28" s="13">
         <f t="shared" si="11"/>
-        <v>0.83907284522618719</v>
+        <v>0.920839271079124</v>
       </c>
       <c r="M28" s="13">
         <f t="shared" si="11"/>
-        <v>0.83046120631064346</v>
+        <v>0.91571984992973454</v>
       </c>
       <c r="N28" s="13">
         <f t="shared" si="11"/>
-        <v>0.80095060022633746</v>
+        <v>0.90064244746086441</v>
       </c>
       <c r="O28" s="13">
         <f t="shared" si="11"/>
-        <v>0.77277771994669875</v>
+        <v>0.89293136762906211</v>
       </c>
       <c r="P28" s="13">
         <f t="shared" si="11"/>
-        <v>0.7889367536405032</v>
+        <v>0.90600297293107124</v>
       </c>
       <c r="Q28" s="13" t="str">
         <f t="shared" si="11"/>
@@ -10796,48 +10802,48 @@
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
-        <v>0.8562535412486959</v>
+        <v>0.94274693651827779</v>
       </c>
       <c r="E30" s="302"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
-        <v>0.86527999760616314</v>
+        <v>0.95222408915481294</v>
       </c>
       <c r="H30" s="30">
         <f t="shared" si="13"/>
-        <v>0.86258858762567259</v>
+        <v>0.94755207855015933</v>
       </c>
       <c r="I30" s="30">
         <f t="shared" si="13"/>
-        <v>0.86732498173691019</v>
+        <v>0.94688424455904585</v>
       </c>
       <c r="J30" s="30">
         <f t="shared" si="13"/>
-        <v>0.82982059802603836</v>
+        <v>0.92432733380909227</v>
       </c>
       <c r="K30" s="30">
         <f t="shared" si="13"/>
-        <v>0.83231211633136815</v>
+        <v>0.94387374263052326</v>
       </c>
       <c r="L30" s="30">
         <f t="shared" si="13"/>
-        <v>0.86048615177771637</v>
+        <v>0.94225257763065318</v>
       </c>
       <c r="M30" s="30">
         <f t="shared" si="13"/>
-        <v>0.8510050744004436</v>
+        <v>0.93626371801953456</v>
       </c>
       <c r="N30" s="30">
         <f t="shared" si="13"/>
-        <v>0.82470077658903318</v>
+        <v>0.92439262382356024</v>
       </c>
       <c r="O30" s="30">
         <f t="shared" si="13"/>
-        <v>0.79843918233414179</v>
+        <v>0.91859283001650516</v>
       </c>
       <c r="P30" s="30">
         <f t="shared" si="13"/>
-        <v>0.8121535522365585</v>
+        <v>0.92921977152712665</v>
       </c>
       <c r="Q30" s="30" t="str">
         <f t="shared" si="13"/>
@@ -10862,18 +10868,18 @@
       </c>
       <c r="C33" s="198">
         <f>AVERAGE(G33:J33)</f>
-        <v>-59357</v>
+        <v>-64464.5</v>
       </c>
       <c r="E33" s="300" t="s">
         <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
-        <v>-58021</v>
+        <v>-67396</v>
       </c>
       <c r="H33" s="191">
         <f>Data!D41</f>
-        <v>-59664</v>
+        <v>-70719</v>
       </c>
       <c r="I33" s="191">
         <f>Data!E41</f>
@@ -10978,18 +10984,18 @@
       </c>
       <c r="C35" s="184">
         <f>C33+C34</f>
-        <v>-72716.5</v>
+        <v>-77824</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="301"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
-        <v>-73236</v>
+        <v>-82611</v>
       </c>
       <c r="H35" s="184">
         <f t="shared" si="14"/>
-        <v>-73633</v>
+        <v>-84688</v>
       </c>
       <c r="I35" s="184">
         <f t="shared" si="14"/>
@@ -11047,18 +11053,18 @@
       </c>
       <c r="C38" s="23">
         <f>ABS(C33/$C$4)</f>
-        <v>1.9231434357303994E-2</v>
+        <v>2.088624425301857E-2</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="299"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
-        <v>1.8871305896579739E-2</v>
+        <v>2.1920520711568022E-2</v>
       </c>
       <c r="H38" s="13">
         <f t="shared" si="15"/>
-        <v>1.8574099180783354E-2</v>
+        <v>2.2015649637399739E-2</v>
       </c>
       <c r="I38" s="13">
         <f t="shared" si="15"/>
@@ -11162,16 +11168,16 @@
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
-        <v>2.3559859771263639E-2</v>
+        <v>2.5214669666978214E-2</v>
       </c>
       <c r="E40" s="302"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
-        <v>2.3819978260318054E-2</v>
+        <v>2.6869193075306337E-2</v>
       </c>
       <c r="H40" s="30">
         <f t="shared" si="17"/>
-        <v>2.2922811829220648E-2</v>
+        <v>2.636436228583703E-2</v>
       </c>
       <c r="I40" s="30">
         <f t="shared" si="17"/>
@@ -11236,43 +11242,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>4.0221113758189396E-2</v>
+        <v>0.28385656114540919</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>4.5954594458567942E-2</v>
+        <v>0.24453337796917085</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>5.3062621644864888E-2</v>
+        <v>0.20958244410427165</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>6.1784593861285396E-2</v>
+        <v>0.19698249645198351</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>2.2469839686961424E-2</v>
+        <v>0.14869452945677122</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>5.2273032677218258E-2</v>
+        <v>0.17932914424300733</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>5.7846462044787869E-2</v>
+        <v>0.19638190173618195</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>4.8621315842920801E-2</v>
+        <v>0.16357516077170417</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>6.5727952869626488E-2</v>
+        <v>0.24937676883242008</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>4.1036703008533994E-2</v>
+        <v>0.17760786301678494</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -11319,7 +11325,7 @@
       </c>
       <c r="C47" s="191">
         <f>-BS!G31*Normalized_FCF!C54</f>
-        <v>0</v>
+        <v>-18601</v>
       </c>
       <c r="E47" s="302"/>
       <c r="G47" s="191">
@@ -11486,7 +11492,7 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>0</v>
+        <v>-18601</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
@@ -11561,7 +11567,7 @@
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
-        <v>5935</v>
+        <v>4.0429430718192903E-2</v>
       </c>
       <c r="H53" s="170"/>
       <c r="I53" s="170"/>
@@ -11581,14 +11587,14 @@
       </c>
       <c r="C54" s="82">
         <f>G54</f>
-        <v>0</v>
+        <v>4.4602115369398357E-2</v>
       </c>
       <c r="E54" s="299" t="s">
         <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
-        <v>0</v>
+        <v>4.4602115369398357E-2</v>
       </c>
       <c r="H54" s="170"/>
       <c r="I54" s="170"/>
@@ -11606,26 +11612,26 @@
       <c r="B55" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C55" s="42" t="e">
+      <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>#DIV/0!</v>
+        <v>5.316119180037191</v>
       </c>
       <c r="E55" s="302"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
-        <v>18.330681146174935</v>
+        <v>3.4556744261061234</v>
       </c>
       <c r="H55" s="42">
         <f t="shared" si="21"/>
-        <v>20.353201616027452</v>
+        <v>4.6370026011400745</v>
       </c>
       <c r="I55" s="42">
         <f t="shared" si="21"/>
-        <v>22.079849722702605</v>
+        <v>6.3370505098694014</v>
       </c>
       <c r="J55" s="42">
         <f t="shared" si="21"/>
-        <v>26.130376881076042</v>
+        <v>8.8822746038087637</v>
       </c>
       <c r="K55" s="42" t="e">
         <f t="shared" si="21"/>
@@ -11903,43 +11909,43 @@
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
-        <v>-257790</v>
+        <v>18900</v>
       </c>
       <c r="H62" s="191">
         <f>Data!D58</f>
-        <v>-270405</v>
+        <v>13571</v>
       </c>
       <c r="I62" s="191">
         <f>Data!E58</f>
-        <v>-265239</v>
+        <v>-1248</v>
       </c>
       <c r="J62" s="191">
         <f>Data!F58</f>
-        <v>-274792</v>
+        <v>-15760</v>
       </c>
       <c r="K62" s="191">
         <f>Data!G58</f>
-        <v>-228802</v>
+        <v>6145</v>
       </c>
       <c r="L62" s="191">
         <f>Data!H58</f>
-        <v>-252302</v>
+        <v>-9767</v>
       </c>
       <c r="M62" s="191">
         <f>Data!I58</f>
-        <v>-248923</v>
+        <v>-2425</v>
       </c>
       <c r="N62" s="191">
         <f>Data!J58</f>
-        <v>-248239</v>
+        <v>-12947</v>
       </c>
       <c r="O62" s="191">
         <f>Data!K58</f>
-        <v>-235164</v>
+        <v>-3158</v>
       </c>
       <c r="P62" s="191">
         <f>Data!L58</f>
-        <v>-251400</v>
+        <v>-15057</v>
       </c>
       <c r="Q62" s="191" t="str">
         <f>Data!M58</f>
@@ -11958,43 +11964,43 @@
       <c r="E63" s="302"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
-        <v>-257790</v>
+        <v>18900</v>
       </c>
       <c r="H63" s="184">
         <f t="shared" si="23"/>
-        <v>-270405</v>
+        <v>13571</v>
       </c>
       <c r="I63" s="184">
         <f t="shared" si="23"/>
-        <v>-265239</v>
+        <v>-1248</v>
       </c>
       <c r="J63" s="184">
         <f t="shared" si="23"/>
-        <v>-274792</v>
+        <v>-15760</v>
       </c>
       <c r="K63" s="184">
         <f t="shared" si="23"/>
-        <v>-228802</v>
+        <v>6145</v>
       </c>
       <c r="L63" s="184">
         <f t="shared" si="23"/>
-        <v>-252302</v>
+        <v>-9767</v>
       </c>
       <c r="M63" s="184">
         <f t="shared" si="23"/>
-        <v>-248923</v>
+        <v>-2425</v>
       </c>
       <c r="N63" s="184">
         <f t="shared" si="23"/>
-        <v>-248239</v>
+        <v>-12947</v>
       </c>
       <c r="O63" s="184">
         <f t="shared" si="23"/>
-        <v>-235164</v>
+        <v>-3158</v>
       </c>
       <c r="P63" s="184">
         <f t="shared" si="23"/>
-        <v>-251400</v>
+        <v>-15057</v>
       </c>
       <c r="Q63" s="184" t="str">
         <f t="shared" si="23"/>
@@ -12128,7 +12134,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12171,50 +12177,50 @@
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
-        <v>0.8562535412486959</v>
+        <v>0.94274693651827779</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="299"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
-        <v>0.86527999760616314</v>
+        <v>0.95222408915481294</v>
       </c>
       <c r="H73" s="6">
         <f t="shared" si="24"/>
-        <v>0.86258858762567259</v>
+        <v>0.94755207855015933</v>
       </c>
       <c r="I73" s="6">
         <f t="shared" si="24"/>
-        <v>0.86732498173691019</v>
+        <v>0.94688424455904585</v>
       </c>
       <c r="J73" s="6">
         <f t="shared" si="24"/>
-        <v>0.82982059802603836</v>
+        <v>0.92432733380909227</v>
       </c>
       <c r="K73" s="6">
         <f t="shared" si="24"/>
-        <v>0.83231211633136815</v>
+        <v>0.94387374263052326</v>
       </c>
       <c r="L73" s="6">
         <f t="shared" si="24"/>
-        <v>0.86048615177771637</v>
+        <v>0.94225257763065318</v>
       </c>
       <c r="M73" s="6">
         <f t="shared" si="24"/>
-        <v>0.8510050744004436</v>
+        <v>0.93626371801953456</v>
       </c>
       <c r="N73" s="6">
         <f t="shared" si="24"/>
-        <v>0.82470077658903318</v>
+        <v>0.92439262382356024</v>
       </c>
       <c r="O73" s="6">
         <f t="shared" si="24"/>
-        <v>0.79843918233414179</v>
+        <v>0.91859283001650516</v>
       </c>
       <c r="P73" s="6">
         <f t="shared" si="24"/>
-        <v>0.8121535522365585</v>
+        <v>0.92921977152712665</v>
       </c>
       <c r="Q73" s="6" t="str">
         <f t="shared" si="24"/>
@@ -12228,50 +12234,50 @@
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
-        <v>0.14374645875130404</v>
+        <v>5.7253063481722218E-2</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="299"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
-        <v>0.13472000239383691</v>
+        <v>4.7775910845187057E-2</v>
       </c>
       <c r="H74" s="65">
         <f t="shared" si="25"/>
-        <v>0.13741141237432739</v>
+        <v>5.2447921449840687E-2</v>
       </c>
       <c r="I74" s="65">
         <f t="shared" si="25"/>
-        <v>0.13267501826308975</v>
+        <v>5.3115755440954163E-2</v>
       </c>
       <c r="J74" s="65">
         <f t="shared" si="25"/>
-        <v>0.1701794019739617</v>
+        <v>7.5672666190907747E-2</v>
       </c>
       <c r="K74" s="65">
         <f t="shared" si="25"/>
-        <v>0.16768788366863185</v>
+        <v>5.6126257369476691E-2</v>
       </c>
       <c r="L74" s="65">
         <f t="shared" si="25"/>
-        <v>0.13951384822228358</v>
+        <v>5.7747422369346837E-2</v>
       </c>
       <c r="M74" s="65">
         <f t="shared" si="25"/>
-        <v>0.14899492559955643</v>
+        <v>6.3736281980465409E-2</v>
       </c>
       <c r="N74" s="65">
         <f t="shared" si="25"/>
-        <v>0.17529922341096682</v>
+        <v>7.5607376176439811E-2</v>
       </c>
       <c r="O74" s="65">
         <f t="shared" si="25"/>
-        <v>0.20156081766585823</v>
+        <v>8.1407169983494843E-2</v>
       </c>
       <c r="P74" s="65">
         <f t="shared" si="25"/>
-        <v>0.18784644776344148</v>
+        <v>7.0780228472873366E-2</v>
       </c>
       <c r="Q74" s="65" t="str">
         <f t="shared" si="25"/>
@@ -12285,18 +12291,18 @@
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
-        <v>2.3559859771263639E-2</v>
+        <v>2.5214669666978214E-2</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="299"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
-        <v>2.3819978260318054E-2</v>
+        <v>2.6869193075306337E-2</v>
       </c>
       <c r="H75" s="6">
         <f t="shared" si="26"/>
-        <v>2.2922811829220648E-2</v>
+        <v>2.636436228583703E-2</v>
       </c>
       <c r="I75" s="6">
         <f t="shared" si="26"/>
@@ -12342,50 +12348,50 @@
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
-        <v>0.1201865989800404</v>
+        <v>3.2038393814744E-2</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="299"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
-        <v>0.11090002413351886</v>
+        <v>2.0906717769880716E-2</v>
       </c>
       <c r="H76" s="65">
         <f t="shared" si="27"/>
-        <v>0.11448860054510672</v>
+        <v>2.6083559164003654E-2</v>
       </c>
       <c r="I76" s="65">
         <f t="shared" si="27"/>
-        <v>0.1115847660516285</v>
+        <v>3.2025503229492901E-2</v>
       </c>
       <c r="J76" s="65">
         <f t="shared" si="27"/>
-        <v>0.14317497566478551</v>
+        <v>4.8668239881731586E-2</v>
       </c>
       <c r="K76" s="65">
         <f t="shared" si="27"/>
-        <v>0.13142122637209019</v>
+        <v>1.9859600072935028E-2</v>
       </c>
       <c r="L76" s="65">
         <f t="shared" si="27"/>
-        <v>0.11540651602913229</v>
+        <v>3.3640090176195549E-2</v>
       </c>
       <c r="M76" s="65">
         <f t="shared" si="27"/>
-        <v>0.12085899904502627</v>
+        <v>3.5600355425935232E-2</v>
       </c>
       <c r="N76" s="65">
         <f t="shared" si="27"/>
-        <v>0.14185789043523137</v>
+        <v>4.2166043200704349E-2</v>
       </c>
       <c r="O76" s="65">
         <f t="shared" si="27"/>
-        <v>0.16315666542890894</v>
+        <v>4.3003017746545545E-2</v>
       </c>
       <c r="P76" s="65">
         <f t="shared" si="27"/>
-        <v>0.15224210615474001</v>
+        <v>3.5175886864171918E-2</v>
       </c>
       <c r="Q76" s="65" t="str">
         <f t="shared" si="27"/>
@@ -12460,7 +12466,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12572,7 +12578,7 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>0</v>
+        <v>6.0266507822196464E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
@@ -12629,50 +12635,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.1201865989800404</v>
+        <v>2.6011743032524355E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.10485005669100184</v>
+        <v>1.4856750327363702E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.14427521196432991</v>
+        <v>5.5870170583226839E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13965356787239225</v>
+        <v>6.0094305050256647E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.17990108300825572</v>
+        <v>8.5394347225201797E-2</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13142122637209019</v>
+        <v>1.9859600072935028E-2</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.11540651602913229</v>
+        <v>3.3640090176195549E-2</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12085899904502627</v>
+        <v>3.5600355425935232E-2</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.14185789043523137</v>
+        <v>4.2166043200704349E-2</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.16315666542890894</v>
+        <v>4.3003017746545545E-2</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.15224210615474001</v>
+        <v>3.5175886864171918E-2</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12686,7 +12692,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.00466497450101E-2</v>
+        <v>6.5029357581310888E-3</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12744,7 +12750,7 @@
       </c>
       <c r="C83" s="298">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
-        <v>0</v>
+        <v>5.0428985684910412E-3</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="299"/>
@@ -12801,50 +12807,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>9.0139949235030312E-2</v>
+        <v>1.4465908705902223E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8280015169640425E-2</v>
+        <v>8.286708806002286E-3</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13628913382198887</v>
+        <v>4.7884092440885803E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.1311509845191684</v>
+        <v>5.159172169703282E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.16635071020882314</v>
+        <v>7.1843974425769203E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>0.12427729745335198</v>
+        <v>1.2715671154196802E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10447499538971335</v>
+        <v>2.2708569536776604E-2</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10791860344862771</v>
+        <v>2.2659959829536669E-2</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.12683623754498044</v>
+        <v>2.7144390310453424E-2</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.14582753943604859</v>
+        <v>2.5673891753685178E-2</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.14047718466102296</v>
+        <v>2.341096537045485E-2</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12908,50 +12914,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>9.0139949235030312E-2</v>
+        <v>1.4465908705902223E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8280015169640425E-2</v>
+        <v>8.286708806002286E-3</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13628913382198887</v>
+        <v>4.7884092440885803E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.1311509845191684</v>
+        <v>5.159172169703282E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.16635071020882314</v>
+        <v>7.1843974425769203E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>0.12427729745335198</v>
+        <v>1.2715671154196802E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10447499538971335</v>
+        <v>2.2708569536776604E-2</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10791860344862771</v>
+        <v>2.2659959829536669E-2</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.12683623754498044</v>
+        <v>2.7144390310453424E-2</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.14582753943604859</v>
+        <v>2.5673891753685178E-2</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.14047718466102296</v>
+        <v>2.341096537045485E-2</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12977,16 +12983,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0754716981132075</v>
+        <v>0.26981132075471698</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0754716981132075</v>
+        <v>0.26981132075471698</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0</v>
+        <v>0.32547169811320753</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -13033,16 +13039,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>251716.43635433962</v>
+        <v>32723.136726064153</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>251716.43635433962</v>
+        <v>32723.136726064153</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>39473.71388283962</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -13088,16 +13094,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.90476126576053284</v>
+        <v>0.7329071203930746</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.83303472357873642</v>
+        <v>1.2843683462620359</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>0.25663277648874366</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -13143,16 +13149,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>0.52016834539178136</v>
+        <v>6.7621884900931573E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.52016834539178136</v>
+        <v>6.7621884900931573E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>8.1571854163711155E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -13280,46 +13286,46 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>0.15070602471333472</v>
+        <v>0.75761050982687039</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-0.30440636712605429</v>
+        <v>-0.7454796703572244</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>1.0574155038689526E-4</v>
+        <v>-9.9978435630356577E-2</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-6.0220488026478058E-2</v>
+        <v>-0.14805431178863182</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.78157393657572505</v>
+        <v>4.5962127008416225</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.19147985206737594</v>
+        <v>-0.58085044546666265</v>
       </c>
       <c r="L97" s="6">
         <f t="shared" si="41"/>
-        <v>-2.0339128568362286E-2</v>
+        <v>-3.0545920895391876E-2</v>
       </c>
       <c r="M97" s="6">
         <f t="shared" si="41"/>
-        <v>4.3645389054155714E-2</v>
+        <v>3.423432475884236E-2</v>
       </c>
       <c r="N97" s="6">
         <f t="shared" si="41"/>
-        <v>6.2756911005234173E-2</v>
+        <v>0.19853074004937676</v>
       </c>
       <c r="O97" s="6">
         <f t="shared" si="41"/>
-        <v>2.4993574289349008E-2</v>
+        <v>0.169243550749127</v>
       </c>
       <c r="P97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13373,14 +13379,14 @@
       </c>
       <c r="C101" s="199">
         <f>BS!G32</f>
-        <v>3</v>
+        <v>2084771</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="303"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
-        <v>3</v>
+        <v>2084771</v>
       </c>
       <c r="H101" s="183">
         <f t="shared" si="42"/>
@@ -13430,7 +13436,7 @@
       </c>
       <c r="C102" s="200">
         <f>BS!C4</f>
-        <v>1</v>
+        <v>79069</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="304"/>
@@ -13487,7 +13493,7 @@
       </c>
       <c r="C103" s="200">
         <f>BS!C6+BS!C7</f>
-        <v>0</v>
+        <v>256595</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="304"/>
@@ -13544,14 +13550,14 @@
       </c>
       <c r="C104" s="199">
         <f>BS!G30</f>
-        <v>1</v>
+        <v>1108478</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="303"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
-        <v>1</v>
+        <v>1108478</v>
       </c>
       <c r="H104" s="183">
         <f>Data!D79</f>
@@ -13601,14 +13607,14 @@
       </c>
       <c r="C105" s="199">
         <f>BS!G27</f>
-        <v>2</v>
+        <v>976293</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="303"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
-        <v>2</v>
+        <v>976293</v>
       </c>
       <c r="H105" s="183">
         <f>Data!D80</f>
@@ -13685,7 +13691,7 @@
       </c>
       <c r="C108" s="94">
         <f>C102/C$4</f>
-        <v>3.2399606377182124E-7</v>
+        <v>2.5618044766374134E-2</v>
       </c>
       <c r="D108" s="26"/>
       <c r="E108" s="303"/>
@@ -13742,7 +13748,7 @@
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>0</v>
+        <v>8.3135769983530464E-2</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="303"/>
@@ -13891,43 +13897,43 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>0.49429456461306293</v>
+        <v>5.8623125834052905</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.36884122524498048</v>
+        <v>1.0498069096441156</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>0.26717388856590707</v>
+        <v>0.67918102692914306</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>0.49385894882749787</v>
+        <v>1.1435028133823559</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>0.64005104575013561</v>
+        <v>6.2555733970648646</v>
       </c>
       <c r="L114" s="334">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>0.49507410622376108</v>
+        <v>2.2776804536951811</v>
       </c>
       <c r="M114" s="334">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>0.56365780803302434</v>
+        <v>2.6844338614647252</v>
       </c>
       <c r="N114" s="334">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>0.63781492393722561</v>
+        <v>2.9802859551087941</v>
       </c>
       <c r="O114" s="334">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>0.76192556289509195</v>
+        <v>4.3277322790172263</v>
       </c>
       <c r="P114" s="334">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>0.58467527247211815</v>
+        <v>3.50833615436696</v>
       </c>
       <c r="Q114" s="334" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -13999,48 +14005,48 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.1201865989800404</v>
+        <v>2.6011743032524355E-2</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.10485005669100184</v>
+        <v>1.4856750327363702E-2</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.14427521196432991</v>
+        <v>5.5870170583226839E-2</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13965356787239225</v>
+        <v>6.0094305050256647E-2</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.17990108300825572</v>
+        <v>8.5394347225201797E-2</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13142122637209019</v>
+        <v>1.9859600072935028E-2</v>
       </c>
       <c r="L117" s="23">
         <f t="shared" si="45"/>
-        <v>0.11540651602913229</v>
+        <v>3.3640090176195549E-2</v>
       </c>
       <c r="M117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12085899904502627</v>
+        <v>3.5600355425935232E-2</v>
       </c>
       <c r="N117" s="23">
         <f t="shared" si="45"/>
-        <v>0.14185789043523137</v>
+        <v>4.2166043200704349E-2</v>
       </c>
       <c r="O117" s="23">
         <f t="shared" si="45"/>
-        <v>0.16315666542890894</v>
+        <v>4.3003017746545545E-2</v>
       </c>
       <c r="P117" s="23">
         <f t="shared" si="45"/>
-        <v>0.15224210615474001</v>
+        <v>3.5175886864171918E-2</v>
       </c>
       <c r="Q117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -14053,12 +14059,12 @@
       </c>
       <c r="C118" s="42">
         <f>C4/C101</f>
-        <v>1028819.0833333334</v>
+        <v>1.4804778318577916</v>
       </c>
       <c r="E118" s="302"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
-        <v>1024854</v>
+        <v>1.4747720493042162</v>
       </c>
       <c r="H118" s="42">
         <f t="shared" si="46"/>
@@ -14107,14 +14113,14 @@
       </c>
       <c r="C119" s="15">
         <f>C101/C105</f>
-        <v>1.5</v>
+        <v>2.135394804633445</v>
       </c>
       <c r="D119" s="11"/>
       <c r="E119" s="306"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
-        <v>1.5</v>
+        <v>2.135394804633445</v>
       </c>
       <c r="H119" s="15">
         <f t="shared" si="47"/>
@@ -14164,50 +14170,50 @@
       </c>
       <c r="C120" s="102">
         <f>C8/C105</f>
-        <v>185475.39988739416</v>
+        <v>0.10128632784202261</v>
       </c>
       <c r="D120" s="103"/>
       <c r="E120" s="305"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
-        <v>170484.5</v>
+        <v>6.5839865696056404E-2</v>
       </c>
       <c r="H120" s="102">
         <f t="shared" si="48"/>
-        <v>0.38362288831748648</v>
+        <v>8.7399533721724709E-2</v>
       </c>
       <c r="I120" s="102">
         <f t="shared" si="48"/>
-        <v>0.39508703488117736</v>
+        <v>0.11339237029599222</v>
       </c>
       <c r="J120" s="102">
         <f t="shared" si="48"/>
-        <v>0.42839348893772222</v>
+        <v>0.14562011962346663</v>
       </c>
       <c r="K120" s="102">
         <f t="shared" si="48"/>
-        <v>0.31313329019002667</v>
+        <v>4.7318854680973348E-2</v>
       </c>
       <c r="L120" s="102">
         <f t="shared" si="48"/>
-        <v>0.3903706786938152</v>
+        <v>0.11378997724953102</v>
       </c>
       <c r="M120" s="102">
         <f t="shared" si="48"/>
-        <v>0.40741716696262736</v>
+        <v>0.12000923443932845</v>
       </c>
       <c r="N120" s="102">
         <f t="shared" si="48"/>
-        <v>0.39201938951139836</v>
+        <v>0.11652440666455911</v>
       </c>
       <c r="O120" s="102">
         <f t="shared" si="48"/>
-        <v>0.37841626377586257</v>
+        <v>9.9738746584186661E-2</v>
       </c>
       <c r="P120" s="102">
         <f t="shared" si="48"/>
-        <v>0.3912296355885711</v>
+        <v>9.0394502197618964E-2</v>
       </c>
       <c r="Q120" s="102" t="str">
         <f t="shared" si="48"/>
@@ -14285,50 +14291,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4315806647079472</v>
+        <v>0.39022679960676571</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.6409463348043278</v>
+        <v>0.22267755261359462</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>3.8262817237893709</v>
+        <v>1.3443333494664984</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>3.8034790809300856</v>
+        <v>1.4961994753089436</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>3.9849825244942001</v>
+        <v>1.7210445462932176</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>2.2874835205018318</v>
+        <v>0.23404828406623165</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>2.708462784052307</v>
+        <v>0.58870847746865951</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>2.7269828301308143</v>
+        <v>0.57259192958344607</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>2.6163869532655806</v>
+        <v>0.55993641909657565</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>2.4610073500642109</v>
+        <v>0.43327643430670931</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>2.4787233167471436</v>
+        <v>0.4130870494830417</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14342,50 +14348,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.60941871295938521</v>
+        <v>9.7801202908963839E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.66189131198103446</v>
+        <v>5.5808910429472336E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.95896785057377709</v>
+        <v>0.33692565149536297</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.95325290248874317</v>
+        <v>0.37498733717016131</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.99874248734190474</v>
+        <v>0.43133948528652066</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.57330414047664957</v>
+        <v>5.8658717811085621E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.67881272783265834</v>
+        <v>0.14754598432798482</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.6834543433911815</v>
+        <v>0.14350674926903409</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.65573607851267679</v>
+        <v>0.14033494212946757</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.61679382207123079</v>
+        <v>0.10859058503927552</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.62123391397171512</v>
+        <v>0.10353058884286759</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15185,7 +15191,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>278213.09983109124</v>
+        <v>44648.408803170038</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15217,7 +15223,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>3477663.7478886405</v>
+        <v>558105.11003962543</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15235,7 +15241,7 @@
       </c>
       <c r="C7" s="226">
         <f>BS!G31</f>
-        <v>0</v>
+        <v>417043</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
@@ -15251,7 +15257,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>-247267.57388162927</v>
+        <v>-104892.27115484935</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15267,7 +15273,7 @@
       </c>
       <c r="C9" s="229">
         <f>BS!H42</f>
-        <v>0</v>
+        <v>24725.9</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -15283,7 +15289,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>3230396.1740070111</v>
+        <v>60895.738884776081</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15311,7 +15317,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>28.233641337632509</v>
+        <v>0.53222835777762956</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15344,7 +15350,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>4.6574870890079501E-2</v>
+        <v>2.0159880081722099E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -15354,7 +15360,7 @@
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H17" s="121"/>
     </row>
@@ -15364,7 +15370,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>33.111517646915438</v>
+        <v>0.69088970064314703</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15399,11 +15405,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>291170.8390356531</v>
+        <v>45548.515370481655</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>2.0159880081722099E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15411,7 +15417,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>269602.62873671582</v>
+        <v>42174.551268964489</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15421,11 +15427,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>304732.08327069477</v>
+        <v>46466.767978251046</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>2.0159880081722099E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -15433,7 +15439,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>261258.64477940221</v>
+        <v>39837.764041710427</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15443,11 +15449,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>318924.94070509233</v>
+        <v>47403.532448477796</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>2.0159880081722099E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -15455,7 +15461,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>253172.90039714816</v>
+        <v>37630.452395847453</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15465,11 +15471,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>333778.8286420583</v>
+        <v>48359.181978089138</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>2.0159880081722099E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15477,7 +15483,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>245337.40328334473</v>
+        <v>35545.442410711752</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15487,11 +15493,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>349324.5344919042</v>
+        <v>49334.097287617602</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>2.0159880081722099E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15499,7 +15505,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>237744.40848682768</v>
+        <v>33575.957654780992</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15509,19 +15515,19 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>365594.2795846017</v>
+        <v>0</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>230386.41075642584</v>
+        <v>0</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15531,19 +15537,19 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>382621.78595440625</v>
+        <v>0</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>223256.13712244009</v>
+        <v>0</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15553,19 +15559,19 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>400442.34623496438</v>
+        <v>0</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>216346.53970771816</v>
+        <v>0</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15575,19 +15581,19 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>419092.89680977835</v>
+        <v>0</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>209650.78876122276</v>
+        <v>0</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15597,19 +15603,19 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>438612.09436964319</v>
+        <v>0</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>203162.26590720372</v>
+        <v>0</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -16059,7 +16065,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>3639635.4879456637</v>
+        <v>569356.44213102071</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16067,11 +16073,11 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.68058319703375303</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1685855.4570183537</v>
+        <v>387494.42763729306</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -16082,7 +16088,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>4035773.5849568034</v>
+        <v>576258.59540930821</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -16103,7 +16109,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>4035773.5849568034</v>
+        <v>576258.59540930821</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16119,11 +16125,11 @@
       </c>
       <c r="E55" s="132">
         <f>C75</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F55" s="132">
         <f>C74</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H55" s="121"/>
     </row>
@@ -16133,19 +16139,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>3477663.7478886396</v>
+        <v>558105.11003962532</v>
       </c>
       <c r="C56" s="124">
-        <v>3477663.7478886396</v>
+        <v>558105.11003962532</v>
       </c>
       <c r="D56" s="124">
-        <v>3589871.3850325947</v>
+        <v>576112.50242008001</v>
       </c>
       <c r="E56" s="124">
-        <v>3705439.591943562</v>
+        <v>585316.97905087203</v>
       </c>
       <c r="F56" s="124">
-        <v>3824515.8412791463</v>
+        <v>594659.20834421832</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16154,19 +16160,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>3477663.7478886396</v>
+        <v>558105.1100396252</v>
       </c>
       <c r="C57" s="124">
-        <v>3477663.7478886396</v>
+        <v>558105.1100396252</v>
       </c>
       <c r="D57" s="124">
-        <v>3702182.3476787573</v>
+        <v>594136.4767633006</v>
       </c>
       <c r="E57" s="124">
-        <v>3949203.7902413355</v>
+        <v>613480.47144409851</v>
       </c>
       <c r="F57" s="124">
-        <v>4221421.1727559101</v>
+        <v>633779.16201923834</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16175,19 +16181,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>3477663.7478886386</v>
+        <v>558105.11003962508</v>
       </c>
       <c r="C58" s="124">
-        <v>3477663.7478886386</v>
+        <v>558105.11003962508</v>
       </c>
       <c r="D58" s="124">
-        <v>3841198.3048652271</v>
+        <v>616446.14259281685</v>
       </c>
       <c r="E58" s="124">
-        <v>4266981.3357135141</v>
+        <v>649247.20507358143</v>
       </c>
       <c r="F58" s="124">
-        <v>4767379.7692634519</v>
+        <v>684776.98263704462</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16196,19 +16202,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>3477663.7478886386</v>
+        <v>558105.11003962508</v>
       </c>
       <c r="C59" s="124">
-        <v>3477663.7478886386</v>
+        <v>558105.11003962508</v>
       </c>
       <c r="D59" s="124">
-        <v>3982833.2715906729</v>
+        <v>639176.11432678753</v>
       </c>
       <c r="E59" s="124">
-        <v>4609013.587577899</v>
+        <v>686685.86845101311</v>
       </c>
       <c r="F59" s="124">
-        <v>5390170.1286607934</v>
+        <v>739667.26571279229</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16217,19 +16223,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>3477663.7478886391</v>
+        <v>558105.11003962508</v>
       </c>
       <c r="C60" s="124">
-        <v>3477663.7478886391</v>
+        <v>558105.11003962508</v>
       </c>
       <c r="D60" s="124">
-        <v>4114561.6499710018</v>
+        <v>660316.24932573037</v>
       </c>
       <c r="E60" s="124">
-        <v>4945926.9913557768</v>
+        <v>722498.84358293016</v>
       </c>
       <c r="F60" s="124">
-        <v>6042835.4894319335</v>
+        <v>793736.06187039556</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16238,19 +16244,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>3477663.7478886386</v>
+        <v>558105.11003962497</v>
       </c>
       <c r="C61" s="124">
-        <v>3477663.7478886386</v>
+        <v>558105.11003962497</v>
       </c>
       <c r="D61" s="124">
-        <v>4230764.4041973483</v>
+        <v>678964.78916049062</v>
       </c>
       <c r="E61" s="124">
-        <v>5261449.379796044</v>
+        <v>755024.98999631556</v>
       </c>
       <c r="F61" s="124">
-        <v>6695417.9092110517</v>
+        <v>844371.96864181082</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16286,11 +16292,11 @@
       </c>
       <c r="E64" s="133">
         <f>E55</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F64" s="133">
         <f>F55</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -16300,23 +16306,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>28.233641337632509</v>
+        <v>0.53222835777762956</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>28.233641337632509</v>
+        <v>0.53222835777762956</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>28.233641337632509</v>
+        <v>0.53222835777762956</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>28.233641337632509</v>
+        <v>0.53222835777762956</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>28.233641337632509</v>
+        <v>0.53222835777762956</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16327,23 +16333,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>28.233641337632498</v>
+        <v>0.53222835777762856</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>28.233641337632498</v>
+        <v>0.53222835777762856</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>29.214335349084344</v>
+        <v>0.68961284887710028</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>30.224400718221471</v>
+        <v>0.7700599141582759</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>31.265126355102474</v>
+        <v>0.85171093680516274</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16354,23 +16360,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>28.233641337632498</v>
+        <v>0.53222835777762745</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>28.233641337632498</v>
+        <v>0.53222835777762745</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>30.195932424746655</v>
+        <v>0.84714226622220512</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>32.354898209852024</v>
+        <v>1.0162086526454124</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>34.734076344604517</v>
+        <v>1.1936190749129678</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16381,23 +16387,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>28.233641337632491</v>
+        <v>0.53222835777762656</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>28.233641337632491</v>
+        <v>0.53222835777762656</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>31.410930977243687</v>
+        <v>1.042128599001223</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>35.13227186953096</v>
+        <v>1.3288096695853451</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>39.505750891219357</v>
+        <v>1.6393396920650289</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16408,23 +16414,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>28.233641337632491</v>
+        <v>0.53222835777762656</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>28.233641337632491</v>
+        <v>0.53222835777762656</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>32.648819655904887</v>
+        <v>1.2407884026238301</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>38.121631503728224</v>
+        <v>1.6560233415380377</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>44.948934540718561</v>
+        <v>2.1190804055266388</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16435,23 +16441,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>28.233641337632495</v>
+        <v>0.53222835777762656</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>28.233641337632495</v>
+        <v>0.53222835777762656</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>33.80012481751448</v>
+        <v>1.4255530436272676</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>41.066252439279438</v>
+        <v>1.9690285089054453</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>50.653225505950779</v>
+        <v>2.5916413287207063</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16461,23 +16467,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>28.233641337632491</v>
+        <v>0.53222835777762545</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>28.233641337632491</v>
+        <v>0.53222835777762545</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>34.815736126019146</v>
+        <v>1.5885411592651333</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>43.823916041315485</v>
+        <v>2.253306814866828</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>56.35679156745762</v>
+        <v>3.034198821233026</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16504,15 +16510,15 @@
       </c>
       <c r="C74" s="143">
         <f>Scenarios!C56</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D74" s="146">
         <f>Scenarios!C55</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>39.505750891219357</v>
+        <v>1.1936190749129678</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16526,15 +16532,15 @@
       </c>
       <c r="C75" s="143">
         <f>Scenarios!C38</f>
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D75" s="146">
         <f>Scenarios!C37</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>32.354898209852024</v>
+        <v>0.7700599141582759</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16553,11 +16559,11 @@
       </c>
       <c r="D76" s="146">
         <f>Scenarios!C25</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>30.195932424746655</v>
+        <v>0.68961284887710028</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16576,11 +16582,11 @@
       </c>
       <c r="D77" s="146">
         <f>Scenarios!C31</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>28.233641337632498</v>
+        <v>0.53222835777762856</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16599,11 +16605,11 @@
       </c>
       <c r="D78" s="146">
         <f>Scenarios!C49</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>28.233641337632491</v>
+        <v>0.53222835777762745</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16724,7 +16730,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0754716981132075</v>
+        <v>0.26981132075471698</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16733,7 +16739,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0754716981132075</v>
+        <v>0.26981132075471698</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16753,7 +16759,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>32.674181937466201</v>
+        <v>0.96290651973134356</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16762,7 +16768,7 @@
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
-        <v>340969</v>
+        <v>64279</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
@@ -16770,7 +16776,7 @@
       </c>
       <c r="E7" s="353" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中國石化(0386.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+        <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中國石化(0386.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
       <c r="F7" s="353"/>
       <c r="H7" s="276">
@@ -16787,7 +16793,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>302168</v>
+        <v>25478</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16809,7 +16815,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>278213.09983109124</v>
+        <v>44648.408803170038</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16875,7 +16881,7 @@
       </c>
       <c r="C13" s="159">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-4.5771520730185866E-2</v>
+        <v>-0.21600924990505743</v>
       </c>
       <c r="E13" s="353"/>
       <c r="F13" s="353"/>
@@ -16893,7 +16899,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.1281447541137325</v>
+        <v>-0.49422024389253916</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16920,7 +16926,7 @@
         <v>134</v>
       </c>
       <c r="C18" s="151">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E18" s="353" t="s">
         <v>338</v>
@@ -16959,7 +16965,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>28.233641337632509</v>
+        <v>0.53222835777762956</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16983,7 +16989,7 @@
       </c>
       <c r="C25" s="167">
         <f>C18</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D25" s="164"/>
       <c r="E25" s="352"/>
@@ -17006,7 +17012,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>30.195932424746655</v>
+        <v>0.68961284887710028</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17041,7 +17047,7 @@
       </c>
       <c r="C31" s="167">
         <f>C18</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D31" s="164"/>
       <c r="E31" s="352"/>
@@ -17064,7 +17070,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>28.233641337632498</v>
+        <v>0.53222835777762856</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17099,7 +17105,7 @@
       </c>
       <c r="C37" s="167">
         <f>C18</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D37" s="164"/>
       <c r="E37" s="352"/>
@@ -17110,7 +17116,7 @@
         <v>135</v>
       </c>
       <c r="C38" s="165">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D38" s="165"/>
       <c r="E38" s="352"/>
@@ -17122,7 +17128,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>32.354898209852024</v>
+        <v>0.7700599141582759</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17149,7 +17155,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>30.235267364344896</v>
+        <v>0.67422536371344111</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17175,7 +17181,7 @@
         <v>134</v>
       </c>
       <c r="C46" s="151">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
@@ -17200,7 +17206,7 @@
       </c>
       <c r="C49" s="167">
         <f>C46</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D49" s="164"/>
       <c r="E49" s="352"/>
@@ -17223,7 +17229,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>28.233641337632491</v>
+        <v>0.53222835777762745</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17258,7 +17264,7 @@
       </c>
       <c r="C55" s="167">
         <f>C46</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D55" s="164"/>
       <c r="E55" s="352"/>
@@ -17269,7 +17275,7 @@
         <v>135</v>
       </c>
       <c r="C56" s="165">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D56" s="165"/>
       <c r="E56" s="352"/>
@@ -17281,7 +17287,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>39.505750891219357</v>
+        <v>1.1936190749129678</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17307,7 +17313,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>30.598710239352997</v>
+        <v>0.69309519897662664</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17344,7 +17350,7 @@
       </c>
       <c r="C64" s="167">
         <f>C18</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
@@ -17356,7 +17362,7 @@
         <v>135</v>
       </c>
       <c r="C65" s="152">
-        <v>4.6574870890079501E-2</v>
+        <v>2.0159880081722099E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -17369,7 +17375,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>33.111517646915438</v>
+        <v>0.69088970064314703</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17432,7 +17438,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-7.0627714511882198E-2</v>
+        <v>-6.2698553441480254</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17465,7 +17471,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0754716981132075</v>
+        <v>0.26981132075471698</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17492,7 +17498,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.7692908855128362</v>
+        <v>0.49000781511666869</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17504,7 +17510,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>13.927496695199357</v>
+        <v>0.31547346334848725</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17514,7 +17520,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>17.696787580712193</v>
+        <v>0.80548127846515594</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17525,7 +17531,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.42164923154334921</v>
+        <v>-0.16215099982581083</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17555,7 +17561,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>1.2976894231064677</v>
+        <v>-0.31663829693844048</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17581,7 +17587,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.3719426974143953</v>
+        <v>0.56835255066387136</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17593,7 +17599,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>17.707586944070023</v>
+        <v>0.40109675866702932</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17603,7 +17609,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>22.07952964148442</v>
+        <v>0.96944930933090068</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17614,7 +17620,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.27841632968281327</v>
+        <v>-0.39872460632005269</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17641,7 +17647,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>5.3486918603257889</v>
+        <v>0.69532994184235264</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17653,7 +17659,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>24.290242721632399</v>
+        <v>0.55020131504393588</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17665,7 +17671,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>29.638934581958189</v>
+        <v>1.2455312568862884</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17675,7 +17681,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>3.1366539631478951E-2</v>
+        <v>-0.79705653527155884</v>
       </c>
     </row>
     <row r="100" spans="2:8">
